--- a/ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx
+++ b/ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx
@@ -9595,7 +9595,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9851,7 +9851,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9972,7 +9972,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10093,7 +10093,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10214,7 +10214,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10335,7 +10335,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx
+++ b/ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx
@@ -6138,7 +6138,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6157,7 +6157,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6263,7 +6263,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6282,7 +6282,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6385,7 +6385,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6404,7 +6404,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6519,7 +6519,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6538,7 +6538,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6606,7 +6606,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6625,7 +6625,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6690,7 +6690,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6709,7 +6709,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6774,7 +6774,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6793,7 +6793,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6848,7 +6848,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6867,7 +6867,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6932,7 +6932,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6951,7 +6951,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7016,7 +7016,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7035,7 +7035,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7100,7 +7100,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7119,7 +7119,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7174,7 +7174,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7193,7 +7193,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7277,7 +7277,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7296,7 +7296,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7380,7 +7380,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7399,7 +7399,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7483,7 +7483,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7502,7 +7502,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7595,7 +7595,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7614,7 +7614,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7679,7 +7679,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7698,7 +7698,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7763,7 +7763,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7782,7 +7782,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7847,7 +7847,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7866,7 +7866,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7921,7 +7921,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7940,7 +7940,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8005,7 +8005,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -8024,7 +8024,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8089,7 +8089,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -8108,7 +8108,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8173,7 +8173,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -8192,7 +8192,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8247,7 +8247,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -8266,7 +8266,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8331,7 +8331,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -8350,7 +8350,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8415,7 +8415,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -8434,7 +8434,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8499,7 +8499,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -8518,7 +8518,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8573,7 +8573,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -8592,7 +8592,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8723,7 +8723,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -8742,7 +8742,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8873,7 +8873,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -8892,7 +8892,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9023,7 +9023,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -9042,7 +9042,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9182,7 +9182,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -9201,7 +9201,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9269,7 +9269,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -9288,7 +9288,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx
+++ b/ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx
@@ -9576,26 +9576,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9832,26 +9832,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9953,26 +9953,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10074,26 +10074,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10195,26 +10195,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10316,26 +10316,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -36910,7 +36910,7 @@
         <v>135</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>35</v>
@@ -39309,7 +39309,7 @@
       </c>
       <c r="C12" s="18" t="n">
         <f aca="false">PL!D71/fx/itc_26*37.59*1000</f>
-        <v>77.0969490852276</v>
+        <v>77.0969490852277</v>
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">PL!E71/fx/itc_27*37.59*1000</f>
@@ -45214,27 +45214,27 @@
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">Units!C12</f>
-        <v>77.0969490852276</v>
+        <v>77.0969490852277</v>
       </c>
       <c r="D10" s="15" t="n">
         <f aca="false">C10/B10-1</f>
-        <v>0.027959321136368</v>
+        <v>0.0279593211363691</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">Units!C12</f>
-        <v>77.0969490852276</v>
+        <v>77.0969490852277</v>
       </c>
       <c r="F10" s="15" t="n">
         <f aca="false">E10/B10-1</f>
-        <v>0.027959321136368</v>
+        <v>0.0279593211363691</v>
       </c>
       <c r="G10" s="18" t="n">
         <f aca="false">Units!C12</f>
-        <v>77.0969490852276</v>
+        <v>77.0969490852277</v>
       </c>
       <c r="H10" s="15" t="n">
         <f aca="false">G10/B10-1</f>
-        <v>0.027959321136368</v>
+        <v>0.0279593211363691</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>675</v>

--- a/ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx
+++ b/ibiden/dist/20261025_Ibiden模型_v0.2.1.xlsx
@@ -11598,6 +11598,82 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">NT$537 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億（欣興模型 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">較新；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tom's Hardware </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">早期報導 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">NT$340 </t>
     </r>
     <r>
@@ -11607,7 +11683,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億、景碩 </t>
+      <t xml:space="preserve">億已過時，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CF02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）、景碩 </t>
     </r>
     <r>
       <rPr>
